--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,68 +462,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AS3020</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HIA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Låg Bloom-nivå</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>AS3024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HIA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Låg Bloom-nivå</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,68 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AR1004</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Låg Bloom-nivå</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>AR1018</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Låg Bloom-nivå</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,64 +472,557 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>AEN2BP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Låg Bloom-nivå</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>AEN2BR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Låg Bloom-nivå</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,0,1,0,0,0]</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EN3062</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>EN3075</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GIT247</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3 av 7 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>AJP23N</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AJP279</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AJP27A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AJP27B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,0,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AKI28Z</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4 av 32 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,1,1,1]</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SS3003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SS3011</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,2,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BP</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,0,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BU</t>
         </is>
@@ -590,15 +626,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
@@ -617,15 +663,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
@@ -644,15 +696,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2018-09-04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>3 av 7 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
         </is>
@@ -671,15 +729,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2020-01-29</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
@@ -698,15 +762,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
@@ -725,15 +795,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
@@ -752,15 +828,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,0,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
@@ -779,15 +861,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
         </is>
@@ -806,15 +894,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>4 av 32 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -833,15 +927,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,1,1,1]</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
@@ -860,15 +960,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
@@ -887,15 +993,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
@@ -914,15 +1026,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
@@ -941,15 +1059,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2016-06-09</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
@@ -968,61 +1092,71 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,2,0,0,0]</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:G20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EN3062</t>
+          <t>AEN2CT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,14 +626,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Låg verbnivå för avancerad kurs</t>
@@ -641,19 +637,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>EN3062</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,10 +659,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>2013-09-03</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Låg verbnivå för avancerad kurs</t>
@@ -674,85 +674,85 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GIT247</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3 av 7 bullets har okänt ledande verb</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,1,0,0,0]</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AJP23N</t>
+          <t>GIT247</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
+          <t>3 av 7 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT247</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AJP279</t>
+          <t>AJP23N</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -773,19 +773,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,1,0,0,0]</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP279</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,19 +806,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP279</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -839,29 +839,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,0,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AKI28Z</t>
+          <t>AJP27B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -872,52 +872,52 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,0,1,0,0,0]</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>AKI28Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4 av 32 bullets har okänt ledande verb</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,1,0,0,0]</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -927,30 +927,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hög verbnivå för grundkurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,1,1,1]</t>
+          <t>4 av 32 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SS3003</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -960,30 +960,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,1,1,1]</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>SS3003</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1009,14 +1009,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1037,19 +1037,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [2,1,1,0,0,0]</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1070,54 +1070,87 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,1,0,0,0]</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>SS3011</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2016-06-09</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>TY3012</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2013-11-07</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2019-12-20</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,2,0,0,0]</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1157,6 +1190,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
